--- a/data/trans_camb/IP19C06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 18,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 12,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 9,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,08</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,68</t>
+          <t>1,67; 15,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,0</t>
+          <t>-7,5; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,0</t>
+          <t>-7,53; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 13,24</t>
+          <t>-2,97; 14,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,0</t>
+          <t>-4,51; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,0</t>
+          <t>-4,39; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 9,88</t>
+          <t>0,18; 11,49</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 13,58</t>
+          <t>1,56; 13,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,22</t>
+          <t>0,61; 5,99</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,43</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 12,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,24</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,06</t>
+          <t>0,51; 5,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,47; 4,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,1</t>
+          <t>0,39; 3,86</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2204,32 +2204,32 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,0</t>
+          <t>-4,63; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,0</t>
+          <t>-5,52; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,0</t>
+          <t>-5,53; 0,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,79</t>
+          <t>-1,39; 0,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,79</t>
+          <t>-1,38; 0,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,0</t>
+          <t>-2,38; 0,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,35</t>
+          <t>-0,48; 1,32</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,38</t>
+          <t>-0,86; 0,38</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,17</t>
+          <t>-0,51; 1,22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,21</t>
+          <t>0,1; 1,26</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,59</t>
+          <t>-0,21; 0,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,42</t>
+          <t>0,22; 1,5</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-61,01; —</t>
+          <t>-38,5; —</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-8,7; —</t>
+          <t>-13,05; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Provincia-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,32</t>
+          <t>0,0; 19,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>0,0; 12,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,89</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,01</t>
+          <t>1,68; 15,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,0</t>
+          <t>-7,56; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 0,0</t>
+          <t>-7,08; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 14,09</t>
+          <t>-2,98; 11,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,0</t>
+          <t>-3,81; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 11,49</t>
+          <t>0,22; 10,9</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,88</t>
+          <t>1,68; 14,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,99</t>
+          <t>0,62; 6,03</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,1</t>
+          <t>0,0; 13,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,58</t>
+          <t>0,49; 5,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,2</t>
+          <t>0,47; 4,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,86</t>
+          <t>0,43; 3,81</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2204,32 +2204,32 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,0</t>
+          <t>-5,53; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,0</t>
+          <t>-5,18; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,0</t>
+          <t>-3,99; 0,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,8</t>
+          <t>-1,34; 0,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,79</t>
+          <t>-1,36; 0,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,32</t>
+          <t>-0,46; 1,3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,38</t>
+          <t>-0,87; 0,38</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,22</t>
+          <t>-0,53; 1,19</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,1; 1,28</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,55</t>
+          <t>-0,24; 0,59</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,5</t>
+          <t>0,2; 1,53</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-38,5; —</t>
+          <t>-57,42; —</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-13,05; —</t>
+          <t>-19,06; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,76</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,68</t>
+          <t>0,0; 18,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>2,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,36; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,54; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,53</t>
+          <t>-2,99; 6,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 11,31</t>
+          <t>1,5; 16,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,0</t>
+          <t>-4,24; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-3,83; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 10,9</t>
+          <t>-0,03; 7,51</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>123,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>492,79%</t>
+          <t>382,92%</t>
         </is>
       </c>
     </row>
@@ -1272,24 +1272,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,42</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,39</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,64; 13,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,03</t>
+          <t>0,72; 6,5</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1493,22 +1493,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,13</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,99</t>
+          <t>0,0; 10,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1599,22 +1599,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1920,24 +1920,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,93</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,19</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,91</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,46; 6,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,26</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,81</t>
+          <t>0,39; 3,92</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,93</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,93</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-0,93</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,75</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>0,78</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>-5,28; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>-5,25; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,67; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,0</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,0</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,8</t>
+          <t>-1,39; 0,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,79</t>
+          <t>-1,64; 0,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>-2,53; 0,0</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -2405,37 +2405,37 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>-0,44; 1,35</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>-0,82; 0,38</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>-0,58; 0,71</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,3</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,38</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,19</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,28</t>
+          <t>0,11; 1,21</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,53</t>
+          <t>0,17; 1,28</t>
         </is>
       </c>
     </row>
@@ -2458,34 +2458,34 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-43,6%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-43,6%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>342,58%</t>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>442,67%</t>
+          <t>397,19%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-57,42; —</t>
+          <t>-61,01; —</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-19,06; —</t>
+          <t>-18,61; —</t>
         </is>
       </c>
     </row>
